--- a/tumores/6. Hipofaringe.xlsx
+++ b/tumores/6. Hipofaringe.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\Ing.Salud\Practicas hospital ORL\Proyecto Practicas\tumores\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\Ing.Salud\Practicas hospital ORL\clasificador-tnm-cabeza-cuello\tumores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E628E41-3913-4CFC-829D-044044FE8D4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C6DCCFB-4BEE-48EE-A073-2ABF6BE4174D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14520" yWindow="0" windowWidth="8520" windowHeight="8880" xr2:uid="{4CA4EF29-18F6-42B8-89A4-4F1C5D6105C8}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4CA4EF29-18F6-42B8-89A4-4F1C5D6105C8}"/>
   </bookViews>
   <sheets>
     <sheet name="TNM" sheetId="1" r:id="rId1"/>
@@ -112,9 +112,6 @@
     <t>Multiples ganglios ipsilateral ≤6 cm y ENE-</t>
   </si>
   <si>
-    <t>Un ganglio ipsilateral &gt;6 cm y ENE-</t>
-  </si>
-  <si>
     <t>≤3 cm y ENE+, &gt;3 cm pero ≤6 cm y ENE-</t>
   </si>
   <si>
@@ -130,12 +127,6 @@
     <t>Ganglio ipsilateral &gt;3 cm ≤6 cm y ENE-</t>
   </si>
   <si>
-    <t>Múltiples ganglios ipsilaterales ≤6 cm</t>
-  </si>
-  <si>
-    <t>Ganglio ipsilateral &gt;6 cm y ENE-</t>
-  </si>
-  <si>
     <t>Ganglio/s linfáticos con ENE+ </t>
   </si>
   <si>
@@ -163,12 +154,6 @@
     <t xml:space="preserve"> ≤2 cm</t>
   </si>
   <si>
-    <t>Ganglios contralaterales ≤6 cm</t>
-  </si>
-  <si>
-    <t>Ganglios bilaterales ≤6 cm</t>
-  </si>
-  <si>
     <t>Contralaterales ≤6 cm y ENE-</t>
   </si>
   <si>
@@ -268,9 +253,6 @@
     <t>🟨 N2c: Ganglios bilaterales ≤6 cm y ENE-</t>
   </si>
   <si>
-    <t>🟦 N3a: Un ganglio ipsilateral &gt;6 cm y ENE-</t>
-  </si>
-  <si>
     <t>🟦 N3b: Uno o más ganglios con ENE+</t>
   </si>
   <si>
@@ -305,6 +287,24 @@
   </si>
   <si>
     <t>Limitado a UN subsitio ( ≤2 cm)</t>
+  </si>
+  <si>
+    <t>🟦 N3a: Un ganglio &gt;6 cm y ENE-</t>
+  </si>
+  <si>
+    <t>Ganglio &gt;6 cm y ENE-</t>
+  </si>
+  <si>
+    <t>Un ganglio &gt;6 cm y ENE-</t>
+  </si>
+  <si>
+    <t>Múltiples ganglios ipsilaterales ≤6 cm y ENE-</t>
+  </si>
+  <si>
+    <t>Ganglios contralaterales ≤6 cm y ENE-</t>
+  </si>
+  <si>
+    <t>Ganglios bilaterales ≤6 cm y ENE-</t>
   </si>
 </sst>
 </file>
@@ -839,7 +839,7 @@
         <v>8</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>9</v>
@@ -848,7 +848,7 @@
         <v>12</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>10</v>
@@ -860,7 +860,7 @@
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="1" t="s">
@@ -876,7 +876,7 @@
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2" t="s">
@@ -892,14 +892,14 @@
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -908,14 +908,14 @@
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -924,14 +924,14 @@
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -940,14 +940,14 @@
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -956,16 +956,16 @@
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
@@ -974,16 +974,16 @@
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>7</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -992,10 +992,10 @@
       </c>
       <c r="B10" s="6"/>
       <c r="C10" s="6" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>13</v>
@@ -1010,7 +1010,7 @@
         <v>15</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>17</v>
@@ -1027,13 +1027,13 @@
         <v>15</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -1044,7 +1044,7 @@
         <v>15</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>19</v>
@@ -1061,13 +1061,13 @@
         <v>15</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>20</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -1078,13 +1078,13 @@
         <v>15</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>21</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>34</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -1095,13 +1095,13 @@
         <v>15</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>22</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>45</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1112,13 +1112,13 @@
         <v>15</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E17" s="5" t="s">
         <v>22</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>46</v>
+        <v>92</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.3">
@@ -1129,13 +1129,13 @@
         <v>15</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>23</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>35</v>
+        <v>88</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
@@ -1146,14 +1146,14 @@
         <v>15</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="D19" s="9"/>
       <c r="E19" s="9" t="s">
         <v>24</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
@@ -1164,7 +1164,7 @@
         <v>16</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>17</v>
@@ -1181,13 +1181,13 @@
         <v>16</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="E21" s="5" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -1198,7 +1198,7 @@
         <v>16</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E22" s="5" t="s">
         <v>19</v>
@@ -1215,16 +1215,16 @@
         <v>16</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>20</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -1235,7 +1235,7 @@
         <v>16</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="E24" s="5" t="s">
         <v>21</v>
@@ -1252,13 +1252,13 @@
         <v>16</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="E25" s="5" t="s">
         <v>22</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -1269,16 +1269,16 @@
         <v>16</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E26" s="5" t="s">
         <v>22</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>14</v>
       </c>
@@ -1286,13 +1286,13 @@
         <v>16</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="E27" s="5" t="s">
         <v>23</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -1303,44 +1303,44 @@
         <v>16</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>24</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
@@ -1369,10 +1369,10 @@
         <v>14</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -1383,7 +1383,7 @@
         <v>18</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D2" s="2">
         <v>0</v>
@@ -1397,10 +1397,10 @@
         <v>18</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -1411,10 +1411,10 @@
         <v>18</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -1425,24 +1425,24 @@
         <v>18</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -1450,27 +1450,27 @@
         <v>7</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
@@ -1478,27 +1478,27 @@
         <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -1506,27 +1506,27 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
